--- a/BDDH文献リスト.xlsx
+++ b/BDDH文献リスト.xlsx
@@ -454,17 +454,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Berzolla et al., 2025, The American Journal of Sports Medicine</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Defining Clinically Important Outcomes for the Modified Harris Hip Score and Nonarthritic Hip Scope for Hip Arthroscopy to Treat Femoroacetabular Impingement at a Minimum 10-Year Follow-up</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>FAISに対して単一術者による初回股関節鏡視下手術を受け，10年フォローアップを有する154例。平均年齢38.8歳，女性63.6%。</t>
         </is>
@@ -486,29 +486,29 @@
 比較対象は+2以下全体？（詳細の記載なし）</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>10年時点の7段階アンカーで+2「improved」以上をPASSと定義し，ROCで最適カットオフを算出。</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="18" t="inlineStr">
         <is>
           <t>分布ベースMCID：mHHS 7.8/8.3/9.5，NAHS 9.5/10.4/10.2（1年/5年/10年）。10年達成率：mHHS 89.0%，NAHS 91.6%。アンカー法10年閾値：mHHS MCID 20.3，SCB 34.0，PASS 81.9；NAHS MCID 24.4，SCB 41.9，PASS 83.1。達成率：mHHS MCID 82.5%，SCB 62.3%，PASS 74.7%；NAHS MCID 79.2%，SCB 42.2%，PASS 69.5%。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Nwachukwu et al., 2020, The American Journal of Sports Medicine</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Defining the Clinically Meaningful Outcomes for Arthroscopic Treatment of Femoroacetabular Impingement Syndrome at Minimum 5-Year Follow-up</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>FAISに対して初回股関節鏡視下手術を受けた283例。平均年齢34.2歳，女性63.3%。1年，2年，5年で評価。</t>
         </is>
@@ -523,34 +523,34 @@
           <t>MCIDは各アウトカムの全体コホートにおける1/2 SDを用いて，1年・2年・5年で個別に算出。対象指標はHOS-ADL，HOS-SS，mHHS，iHOT-12。</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>アンカー質問：「Since your surgery, has there been any change in your daily functioning and nonsporting activities related to your treated hip?」。 “A very great deal better”，“A great deal better”，“A good deal better”をmuch improved群，“Almost the same, hardly any better”，“No change”，“Almost the same, hardly any worse”をno change群とし，ROCでSCB閾値を算出。</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>アンカー質問：「現在の状態は満足できるか」に対するyes/no。ROCでPASS閾値を算出。</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>MCID：HOS-ADL 8.8/9.7/10.2，HOS-SS 13.9/14.3/15.2，mHHS 6.9/9.2/11.4，iHOT-12 15.1/13.9/15.1（1年/2年/5年）。SCB：HOS-ADL 89.7/91.9/94.6，HOS-SS 78.1/77.9/85.8，mHHS 86.9/85.8/94.4，iHOT-12 72.6/76.8/87.5。PASS：HOS-ADL 89.7/88.2/92.2，HOS-SS 72.2/76.4/80.9，mHHS 84.8/83.25/83.6，iHOT-12 69.1/72.2/74.3。達成率：MCID 82.6/87.3/79.3%，PASS 67.6/74.9/67.5%，SCB 62.3/67.2/56.6%。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Vogel et al., 2024, The American Journal of Sports Medicine</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>The Promising 2-Year Performance of the Patient-Reported Outcomes Measurement Information System in Primary Hip Arthroscopy for Femoroacetabular Impingement Syndrome</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>FAISに対して初回股関節鏡視下手術を受け，術前および2年時点のPROMが揃った65例。平均年齢36.9歳，女性72.3%。</t>
         </is>
@@ -565,34 +565,34 @@
           <t>MCIDは術前から2年時点までのPROM変化量の1/2 SD。対象はPROMIS-PI，PROMIS-PF，HOS-ADL，HOS-SS，iHOT-12，VAS pain。</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>算出なし。</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>2年以上の時点でyes/noのPASSアンカー質問を用い，ROCを作成。AUC 0.70以上を臨床的に有用と判断し，Youden J statisticで閾値を決定。</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>MCID：PROMIS-PI −4.7，PROMIS-PF 5.8，HOS-ADL 10.1，HOS-SS 13.8，VAS pain −13.8，iHOT-12 14.0。PASS：PROMIS-PI 57.0，PROMIS-PF 45.6，HOS-ADL 78.7，HOS-SS 76.4，VAS pain 25.5，iHOT-12 67.4。達成率：PROMIS-PI MCID 65%/PASS 65%，PROMIS-PF 60%/58%，HOS-ADL 75%/67%，HOS-SS 79%/62%，iHOT-12 67%/60%，VAS pain 78%/61%。any legacy PROMではMCID 87%，PASS 70%；either PROMIS CATではMCID 74%，PASS 69%。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Bodendorfer et al., 2021, The American Journal of Sports Medicine</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Defining Clinically Significant Improvement on the Patient-Reported Outcomes Measurement Information System Test at 1-Year Follow-up for Patients Undergoing Hip Arthroscopy for the Treatment of Femoroacetabular Impingement Syndrome</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>FAISに対して初回股関節鏡視下手術を受け，術前・1年時点のPROMを有する124例。平均年齢32.7歳。</t>
         </is>
@@ -602,39 +602,39 @@
           <t>分布ベース法</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>MCIDは1年時点の各PROMについて，術前スコアの1/2 SDで算出。対象はPROMIS-PF，PROMIS-PI，HOS-ADL，HOS-SS，mHHS，iHOT-12。</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>1年時点で日常機能・非スポーツ活動の変化を尋ねるアンカーを使用。 “A very great deal better”，“A great deal better”，“A good deal better”をmuch improved群，“Almost the same, hardly any better”，“No change”，“Almost the same, hardly any worse”をno change群とし，ROCで算出。</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>1年時点で「現在の状態は満足できるか」に対するyes/noを用い，ROCとYouden Jで閾値を算出。AUC 0.70以上を臨床的に有用と判断。</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>MCID/SCB/PASS：PROMIS-PI −3.1/51.9/53.7，PROMIS-PF 3.3/49.9/47.0，HOS-ADL 8.5/90.4/87.1，HOS-SS 10.5/77.9/73.6，mHHS 7.5/80.3/75.9，iHOT-12 8.8/73.6/64.1。達成率（MCID/PASS/SCB）：PROMIS-PI 81.5/60.1/51.6%，PROMIS-PF 77.4/64.5/54.0%，HOS-ADL 84.7/70.5/58.0%，HOS-SS 80.8/66.7/58.9%，mHHS 84.7/73.7/68.4%，iHOT-12 77.9/73.6/63.7%。Any CSO：PROMIS 89.0/71.8/62.1%，legacy 87.1/76.6/71.8%。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Martin et al., 2019, Arthroscopy</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Minimal Clinically Important Difference and Substantial Clinical Benefit Values for the 12-Item International Hip Outcome Tool</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>股関節鏡視下手術を受けた患者733例。平均年齢35.3歳，女性73%。術後335–395日で評価。対象はFAI 92%，labral pathology 90%。</t>
         </is>
@@ -649,101 +649,101 @@
           <t>MCIDは1年時点のiHOT-12変化量の1/2 SD。</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>アンカーは現在の機能レベルの4カテゴリー評価：「severely abnormal」「abnormal」「nearly normal」「normal」。術前から術後のカテゴリー改善の有無でimproved群とnot improved群に分類し，ROCでSCB変化量を算出。さらに術後絶対値としてnormal機能を識別する閾値，abnormal/severely abnormal機能を識別する閾値も算出。</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>算出なし。</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>iHOT-12 MCID 13点。SCB変化量 28点。術後絶対値では，86点以上でnormal function，56点以下でabnormal functionを識別。術後時点で536例73%がimproved群，197例27%がnot improved群。PASSは未定義。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Cheng et al., 2025, The American Journal of Sports Medicine</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Defining the Minimal Clinically Important Improvement, Substantial Clinical Benefit, and Patient Acceptable Symptom State for the iHOT-12, HOOS, and HOOSglobal in the Nonoperative Management of Nonarthritic Hip-Related Pain</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>非手術管理を選択した15–40歳のnonarthritic hip-related pain患者61例。平均年齢28歳，女性82%。12か月評価。</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>MCIIはアンカー法で算出。</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>MCIIは9段階GROCを使用。質問は12か月前と比較した股関節全体の状態。選択肢は−4「a great deal worse」から+4「a great deal better」。MCIIは+1「slightly better」以上。ROCでベースラインから12か月までの変化量に基づきカットオフ算出。</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>9段階GROCで，SCBは+3「quite a bit better」以上。ROCで算出。</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>PASSはyes/no質問：「現在の状態は満足できるか」。ROCで算出。</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>MCII：iHOT-12 14，HOOS Symptoms 5，Pain 5，ADL 4，Sport/Rec 13，QOL 6，HOOSglobal 5。SCB：iHOT-12 18，HOOS Symptoms 10，Pain 23，ADL 10，Sport/Rec 19，QOL 25，HOOSglobal 12。PASS：iHOT-12 63，HOOS Symptoms 75，Pain 75，ADL 87，Sport/Rec 63，QOL 50，HOOSglobal 65。アンカー基準上の達成者はMCII 46例75%，SCB 25例41%，PASS 45例74%。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Chéret et al., 2025, Musculoskeletal Science and Practice</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Minimal important change in the Hip Disability and Osteoarthritis Outcome Score and the European Quality of Life 5 Dimensions in adults with hip osteoarthritis after 12 weeks of exercise</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>股関節OA患者150例。12週間の監督下グループ運動療法後に評価。平均年齢65.1歳，女性66%。</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>MICはアンカー法のpredictive modeling approachで算出。</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>7段階GRCSを使用。痛み，ADL，QoLの3領域について「運動介入前と比較してどうか」を質問。6または7を“importantly improved”，1–5を“not importantly improved”に分類。測定指標の変化量とGRCSの相関が0.30以上の場合のみMIC解析。MICpredはロジスティック回帰に基づくpredictive modelingで算出し，改善者割合&gt;50%による過大推定を考慮してMICpred-adjustedも提示。</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>算出なし。</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>算出なし。</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>MICpred：HOOS Symptoms 7.24，Pain 8.19，ADL 7.23，Sport/Rec 9.95，QOL 6.11，EQ-5D-5L index 0.054，EQ-VAS 4.83。MICpred-adjusted：HOOS Symptoms 6.84，Pain 7.84，ADL 6.72，Sport/Rec 9.27，QOL 5.60，EQ-5D-5L index 0.049，EQ-VAS 4.26。パフォーマンステスト，筋力・パワーテストはGRCSとの相関&lt;0.30のためMIC解析から除外。SCB/PASSおよびMIC達成率は報告なし。</t>
         </is>
@@ -803,7 +803,7 @@
           <t>④方法</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>⑤症例数</t>
         </is>
@@ -813,7 +813,7 @@
           <t>⑥結果</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>⑦研究限界</t>
         </is>
@@ -830,37 +830,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Chapman RS, Allahabadi S, Fenn TW, Larson JH, Beals CT, Kaplan DJ, Nho SJ. 2024. Am J Sports Med 52(7):1744-1752</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Outcome Scores and Survivorship of Patients Undergoing Primary Hip Arthroscopy With Borderline Hip Dysplasia: A Propensity-Matched Study With Minimum 10-Year Follow-up</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>FAISに対し初回股関節鏡を施行（2012/1〜2013/2）。BHD群（LCEA 18–25°）vs BHDなし対照群</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>後ろ向きコホート（抄録上Level 2）／年齢・性別・BMIで1:3傾向スコアマッチング／術前と術後10年でHOS-ADL・HOS-SS・mHHS・iHOT-12・VAS疼痛・満足度を比較／MCID・PASS達成率の群間比較／Kaplan-Meier生存分析（再手術・THA移行）</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>BHD群28例（女性20例、年齢30.8±10.8歳）vs 対照84例（計112例）、平均追跡10.3±0.3年</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>両群とも全PROが術前から有意改善（P&lt;.001）。PROスコアはHOS-SSのみBHD群低値（62.9±31.9 vs 80.1±26.0、P=.030）。MCID達成率は全PROで群間差なし（例：HOS-ADL 76.2% vs 67.9%、mHHS 76.5% vs 67.9%）。PASS達成率はBHD群で有意に低値（HOS-ADL 39.1% vs 77.4%、HOS-SS 45.5% vs 84.7%、VAS疼痛 50.0% vs 78.5%）。再手術率・生存率に有意差なし（P=.645）</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>後ろ向き／BHD群28例と小規模で検出力不足の可能性／単施設・単一術者系の手術例のみで保存療法へ外挿不可／10年追跡の脱落・選択バイアス（デザイン由来、要原著Discussion確認）</t>
         </is>
@@ -877,22 +877,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Beck EC, Drager J, Nwachukwu BU, Rasio J, Jan K, Chahla J, Nho SJ. 2020. Am J Sports Med 48(7):1616-1624</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Patients With Borderline Hip Dysplasia Achieve Clinically Significant Improvement After Arthroscopic Femoroacetabular Impingement Surgery: A Case-Control Study With a Minimum 5-Year Follow-up</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>FAISに対し関節包閉鎖を伴う初回股関節鏡を施行（2012/1〜2014/8、連続症例）。BHD群（LCEA 20–25°）vs 正常被覆群（LCEA 25–40°）</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>後ろ向きコホート（Level 3）／年齢（±1歳）・BMI（±5）で1:2マッチング／術前と術後5年のPRO（HOS-ADL・HOS-SS・mHHS）／MCID・PASSを算出し群間比較／BHD群内でMCID・PASS達成の予測因子を二項ロジスティック回帰で検討</t>
         </is>
@@ -902,12 +902,12 @@
           <t>BHD群88例 vs 対照176例（計264例）</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>両群ともPROが5年で有意改善、群間差なし（P&gt;.05）。少なくとも1指標でのMCID達成86.6% vs 85.2%（P=.804）、PASS達成76.0% vs 73.7%（P=.675）。BHD群MCID：HOS-ADL 9.6・HOS-SS 14.1・mHHS 9.5。PASS閾値：90.9・76.6・81.9。MCID予測因子：身体活動あり（OR 27.59）・女性（OR 14.64）。PASS予測因子：ランニング習慣（OR 11.1）・女性（OR 7.6）・術前LCEA大（OR 2.3）</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>後ろ向き／単施設／関節包閉鎖を行った手術例のみで保存療法へ外挿不可／BHD群88例に対し予測因子のORが大きく推定が不安定な可能性（デザイン由来、要原著Discussion確認）</t>
         </is>
@@ -924,22 +924,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Cancienne JM, Beck EC, Kunze KN, Chahla J, Suppauksorn S, Nho SJ. 2019. Arthroscopy 35(12):3240-3247</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Functional and Clinical Outcomes of Patients Undergoing Revision Hip Arthroscopy With Borderline Hip Dysplasia at 2-Year Follow-up</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>FAISに対し股関節鏡を施行（2012/1〜2016/1、単一術者）。①BHD再手術群（LCEA 18–25°）②BHD初回手術群 ③非BHD再手術群（LCEA &gt;25°）</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>後ろ向きコホート（抄録上Level III, case-control）／年齢・BMIで2:1マッチング／患者背景・併存症・術前スコアを比較／術後2年のHOS-ADL・HOS-SS・mHHSを多変量回帰で群間比較／MCID・PASS達成の予測因子を二項回帰で検討</t>
         </is>
@@ -949,12 +949,12 @@
           <t>抄録に記載なし（要原著確認）。年齢：BHD再手術群29.1±8.8歳、BHD初回群28.9±8.5歳、非BHD再手術群29.15±8.6歳</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>3群間で年齢・BMIに差なし。術後2年の臨床成績はBHD再手術群と他2群で有意差なし。ただしHOS-SSのPASS達成率はBHD再手術群で有意に低値（vs BHD初回群 P=.047、vs 非BHD再手術群 P=.031）</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>統計的検出力不足（抄録明記）／後ろ向き／単一術者／再手術例のみで保存療法へ外挿不可（デザイン由来）</t>
         </is>
@@ -1911,104 +1911,944 @@
       </c>
     </row>
     <row r="25">
-      <c r="E25" s="13" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="12" t="n"/>
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Cheng AL, Collis RW, McCullough AB, Bui M, Brady BK, Schuelke MJ, Clohisy JC, Colditz GA, Prather H. 2022. PM R 14(5):575-586</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Rate of continued conservative management versus progression to surgery at minimum 1-year follow-up in patients with pre-arthritic hip pain</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>単一の三次医療機関で、保存療法医または股関節外科医の初診を受け、関節症のない股関節痛（pre-arthritic hip pain）と診断された13–40歳。保存療法（理学療法・活動修正・消炎鎮痛薬・関節内注射）は決まったプロトコルのない実臨床（原著本文）</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>後ろ向きコホート／主要アウトカム：最低1年での手術移行率／全体とあらかじめ定めた画像サブグループ（cam FAI［α角≥50°；軽度50–63°・重度&gt;63°］、臼蓋形成不全［LCEA ≤25°；borderline 20–25°、dysplasia &lt;20°］、関節唇損傷確定例）ごとに、手術移行の予測因子を多重ロジスティック回帰で検討（原著本文）</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>713例830股（平均25.4±8.1歳、女性72.7%）、平均追跡2.6年（1.0–4.8年）</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>全体の手術移行率は51.7%（429/830股）。全体での手術移行の予測因子：若年（OR 0.95/歳）、6か月超の疼痛持続（OR 1.87–2.03）、身体機能の低さ（PROMIS 1点あたりOR 0.96）、臨床診断FAI（OR 3.47）・臼蓋形成不全（OR 2.75）・関節唇損傷（OR 10.71）。LCEA &lt;20°はすべてのサブグループで手術移行を増加（OR 2.05–8.47）。重度cam FAI（α角&gt;63°）ではα角が大きいほど手術移行が増加（OR 1.03/度）。borderline dysplasia（LCEA 20–25°）サブグループは152股で手術移行率48.0%、既知の関節唇損傷のOR 19.40、α角のOR 0.99（原著本文Table 5、有意性の表記は要原著確認）。結論：約半数は1年以上手術に移行せず、多くの患者で保存療法の試行は妥当</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：他院での手術移行は記録がなければ非移行として扱った／三次医療機関のため手術移行率を過大評価している可能性／手術に移行しなかった患者が症状を十分にコントロールできていたかは評価できない（手術適応外と判断された可能性）。加えて保存療法の内容が標準化されていない</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/pmrj.12746</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／臨床成績</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="E26" s="13" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="12" t="n"/>
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Casartelli NC, Bizzini M, Maffiuletti NA, Sutter R, Pfirrmann CW, Leunig M, Naal FD. 2019. Arthritis Care Res (Hoboken) 71(8):1074-1083</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Exercise Therapy for the Management of Femoroacetabular Impingement Syndrome: Preliminary Results of Clinical Responsiveness</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>FAIS患者</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>前向き研究／12週間の半標準化・漸増型運動療法／18週時のGlobal Treatment Outcome（股関節痛）で反応群・非反応群に分類／HOS-ADL・HOS-Sportを0・6・12・18週、股関節筋力（ダイナモメーター）と動的骨盤コントロール（動画解析）を0・12・18週に評価／ベースラインに画像で股関節形態を評価</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>31例（平均24歳）</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>反応群16例（52%）、非反応群15例（48%）。反応群のみHOS-ADLが10点（95%CI 7–14）、HOS-Sportが20点（95%CI 15–25）改善し、股関節外転筋力も0.27 Nm/kg改善（いずれもP&lt;.001）。良好な動的骨盤コントロールを示す割合は反応群でのみ増加（44%、P=.029）。重度cam形態の割合は非反応群で高い（40% vs 6%、P=.037）。結論：FAIS患者の半数が短期的に運動療法の恩恵を受け、外転筋力と動的骨盤コントロールの改善が良好な成績と関連し、重度cam形態は不良な成績と関連</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>抄録上preliminary（予備的）な結果／31例と小規模で18週の短期評価／対照群なし／BDDHは対象外で、臼蓋被覆との関連は不明（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/acr.23728</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／臨床成績</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="E27" s="13" t="n"/>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="12" t="n"/>
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Saito M, Kobayashi N, Honda H, Kamono E, Yukizawa Y, Choe H, Ike H, Kumagai K, Inaba Y. 2024. Arthroscopy 40(3):766-776.e1</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Physical Therapy May Not Be Successful for Patients With Cam-Type Femoroacetabular Impingement Syndrome and May Result in Insufficient Hip Range of Motion When Femoral Anteversion Is Less Than 16° and α-Angle Is Greater Than 65°</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>鏡視下cam切除を受けたcam型FAIS連続症例の術前CT</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>CTに基づく動的コンピュータシミュレーション／仰臥位機能的骨盤面から骨盤を10°後傾させた3次元モデルを作成（理学療法による骨盤可動性改善を想定）／後傾後の90°屈曲位内旋の改善が&gt;10°の有効群と≤10°の無効群に分類／Tönnis grade・LCEA・臼蓋荷重部傾斜角・臼蓋前捻（中央・頭側）・大腿骨前捻・α角などを比較し、単変量・多変量ロジスティック回帰で無効の関連因子を検討</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>71例（男58例、女13例、平均41.4±14.6歳）：有効群13股、無効群58股</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>単変量解析で術前の90°屈曲位内旋可動域、大腿骨前捻、α角が2群間で有意差。多変量解析で可動域改善不十分の関連因子は大腿骨前捻&lt;16°（OR 7.4、95%CI 1.6–35、P=.012）とα角&gt;65°（OR 6.7、95%CI 1.2–37、P=.027）。結論：大きなcam変形と小さい大腿骨前捻を有するcam型FAISでは、保存療法で骨盤可動性を改善しても可動域改善が不十分で、cam変形に対する手術が有益な可能性</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>実際の理学療法の介入・臨床成績ではなく骨盤後傾を想定したシミュレーション／手術例（cam切除例）のみが対象／男性が大半／軟部組織を考慮していない／BDDHに限定した解析ではない（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.arthro.2023.07.012</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／病態</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="E28" s="13" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="12" t="n"/>
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Pennock AT, Bomar JD, Johnson KP, Randich K, Upasani VV. 2018. Am J Sports Med 46(14):3415-3422</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Nonoperative Management of Femoroacetabular Impingement: A Prospective Study</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>手術既往がなく、鼠径部痛・インピンジメントテスト陽性・画像上のFAIを有するFAIS患者（青年期中心、2013〜2016に前向き登録）</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>前向きコホート（Level 2）／段階的プロトコル：①安静・理学療法・活動修正 → ②症状が続けば画像ガイド下関節内ステロイド注射 → ③再発すれば鏡視下手術／12・24か月でアウトカムを収集／手術移行の危険因子とFAI型・治療別の成績を解析</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>76例93股（平均15.3歳、10.4–21.4歳）、平均追跡26.8±8.3か月</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>65股（70%）が理学療法・安静・活動修正のみ、11股（12%）がステロイド注射まで、17股（18%）が鏡視下手術。3群ともmHHS（平均20.3±16.8点改善）・NAHS（13.2±15.5点改善）が同程度に改善（P=.961、P=.975）。cam型および混合型FAIは、pincer型単独と比べてmHHSのMCID達成が4.0倍（P=.004）、手術移行も4.4倍（P=.05）。チームスポーツ選手は個人競技選手より競技復帰が3.0倍（P=.045）。結論：青年期FAISの82%は保存療法で管理可能</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>対象が青年期（平均15.3歳）で成人への外挿に限界／対照群なし／保存療法の内容が段階的で標準化の程度は不明／臼蓋形成不全の扱いは抄録に記載なし（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/0363546518804805</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／臨床成績</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="E29" s="13" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="12" t="n"/>
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Zogby AM, Bomar JD, Johnson KP, Upasani VV, Pennock AT. 2021. Am J Sports Med 49(11):2960-2967</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Nonoperative Management of Femoroacetabular Impingement in Adolescents: Clinical Outcomes at a Mean of 5 Years: A Prospective Study</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>股関節痛で受診し、少なくとも片側でインピンジメントサインが陽性の青年期患者（Pennock 2018と同じ前向きコホートの5年成績）</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>前向きコホート（Level 2）／段階的プロトコル（安静・理学療法・活動修正 → 関節内ステロイド注射 → 鏡視下手術）／初診後平均1・2・5年でmHHS・NAHSを収集</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>100例（女性62%、平均15歳）、5年時に51例69股を追跡</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>登録時mHHS 69.6±12.9、NAHS 75.5±15.2 → 5年時89.5±10.8、88.1±12。5年時のmHHS・NAHSは活動修正＋理学療法群・注射群・鏡視下手術群で差なし（P&gt;.6）、mHHSのMCID達成割合も治療経過で差なし（P=.99）。FAI型（cam・pincer・混合）間でもmHHS・NAHS・MCID達成割合に差なし（P=.64）。手術を要した12股中11股は2年以内に手術。2年から5年でスコアの低下なし（P&gt;.3）。結論：青年期FAISの大多数で保存療法は有効で、改善は5年持続</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>5年時の追跡率が約半数（100例中51例）で脱落バイアスの可能性／青年期のみで成人への外挿に限界／対照群なし（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/03635465211030512</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／臨床成績</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="E30" s="13" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="12" t="n"/>
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Kawai M, Tateda K, Ikeda Y, Kosukegawa I, Nagoya S, Katayose M. 2022. Hip Pelvis 34(1):45-55</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>The Short-term Outcomes of Physiotherapy for Patients with Acetabular Labral Tears: An Analysis according to Severity of Injury in Magnetic Resonance Imaging</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>理学療法を受けた有症候性の股関節唇損傷患者（日本）</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>後ろ向き研究／3-T MRIで関節唇損傷の重症度をCzerny分類で評価／微小不安定性の臨床所見と関節外病変の有無を評価／理学療法前後のiHOT-12を比較し、重症度別に効果を検討</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>35例</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>iHOT-12は平均4.7か月で44.0→73.6に有意改善。Czerny stage I・IIでは介入後に有意改善（いずれもP&lt;.01）したが、stage IIIでは有意差なし（P=.061）。微小不安定性所見陽性7例（20.0%）、関節外病変の所見22例（62.9%）。8例（22.9%）が保存療法無効で手術に移行し、うち4例がstage III。結論：関節唇損傷に対する理学療法は短期的にiHOT-12を改善するが、重度損傷では改善が乏しい可能性があり、損傷重症度の評価が治療方針の決定に有用</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：3-T MRIの関節唇損傷の感度・特異度に限界があり、正常な関節唇溝を損傷と誤認した可能性／疼痛の主因が関節唇損傷かどうかの同定が不十分（63%に関節外病変の所見）で、今後は関節内注射の効果を組み入れ基準に加えるべき。加えて小規模・短期・対照群なし／骨形態（臼蓋被覆・Cam）別の解析なし</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5371/hp.2022.34.1.45</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／臨床成績</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="E31" s="13" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="12" t="n"/>
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>Hunt D, Prather H, Harris Hayes M, Clohisy JC. 2012. PM R 4(7):479-487</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Clinical outcomes analysis of conservative and surgical treatment of patients with clinical indications of prearthritic, intra-articular hip disorders</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>大学病院外来で、症状・疼痛分布・身体所見から関節症前の関節内股関節疾患（関節唇損傷・臼蓋形成不全・FAIを含む）と判断された連続症例</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>前向き観察研究／全例に指導下の保存療法（活動修正・鎮痛薬・理学療法など）を実施／3か月後も機能制限が残り、診断的関節内注射で症状が軽減し、MR関節造影で手術適応病変がある例は手術へ／Numeric Pain Score、SF-12、mHHS、WOMAC、NAHS、Baecke身体活動質問票、手術選択を評価</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>58例登録（男9例、女49例、平均35±11歳）、52例が完遂</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>23例（44%）が保存療法に満足し、29例（56%）が手術を選択。両群とも1年でベースラインから全アウトカムが同程度に有意改善（P=.03〜.0001）。手術選択群はベースラインの活動性スコアが高かった（P=.02）。結論：関節症前の関節内股関節疾患では、手術の前に保存療法を試みるべき</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：長期追跡がない／MR関節造影を全例で撮影しておらず、構造的診断に基づく均質な集団ではない／理学療法の受診回数にばらつきがある。加えて診断別（形成不全・FAI）の成績は抄録に記載なし</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.pmrj.2012.03.012</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／臨床成績</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="E32" s="13" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="12" t="n"/>
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>Griffin DR, Dickenson EJ, Wall PDH, Achana F, Donovan JL, Griffin J, Hobson R, Hutchinson CE, Jepson M, Parsons NR, Petrou S, Realpe A, Smith J, Foster NE; FASHIoN Study Group. 2018. Lancet 391(10136):2225-2235</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Hip arthroscopy versus best conservative care for the treatment of femoroacetabular impingement syndrome (UK FASHIoN): a multicentre randomised controlled trial</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>英国NHS 23病院の16歳以上のFAIS患者（股関節痛＋画像上のcamまたはpincer形態、OAなし、股関節鏡が有益と考えられる例）</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>多施設・実践的・評価者盲検RCT／股関節鏡 vs personalised hip therapy（個別化・監督下・漸増型の理学療法士主導プログラム）を1:1で割付（インピンジメント型と施設で層別化）／主要アウトカム：割付12か月後のiHOT-33（ITT解析）</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>348例（股関節鏡171例、理学療法177例）、12か月の追跡92%（319例）</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>iHOT-33は股関節鏡群39.2→58.8、理学療法群35.6→49.7に改善。調整後の群間差6.8点（95%CI 1.7–12.0、P=.0093）で股関節鏡が優位で、MCID（6.1点）を上回った。有害事象は股関節鏡群72%、理学療法群60%（最多は筋肉痛）。重篤な有害事象7件（股関節鏡群の6件中5件が治療関連）。結論：両治療とも股関節関連QOLを改善し、股関節鏡の方が臨床的に意味のある大きな改善</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：患者・治療者は割付を盲検化できていない／手術待機の遅れにより、股関節鏡群は主要評価時点（割付12か月後）で術後の回復期間が短い例が多かった。加えて12か月の短期評価（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/S0140-6736(18)31202-9</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／手術療法</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="E33" s="13" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="12" t="n"/>
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Palmer AJR, Ayyar Gupta V, Fernquest S, Rombach I, Dutton SJ, Mansour R, Wood S, Khanduja V, Pollard TCB, McCaskie AW, Barker KL, Andrade TJMD, Carr AJ, Beard DJ, Glyn-Jones S; FAIT Study Group. 2019. BMJ 364:l185</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Arthroscopic hip surgery compared with physiotherapy and activity modification for the treatment of symptomatic femoroacetabular impingement: multicentre randomised controlled trial</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>英国NHS 7施設の18–60歳で、臨床所見と画像で確認された症候性FAI。手術既往、過去12か月以内のFAI向け理学療法完了、OA（Kellgren-Lawrence grade ≥2）、臼蓋形成不全（CE角&lt;20°）は除外</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>2群並行・評価者盲検・実践的RCT／鏡視下手術 vs 理学療法＋活動修正（体幹安定性と運動コントロールを重視した目標設定型の個別プログラム、5か月で最大8回）／主要アウトカム：割付8か月後のHOS-ADL（群間MCID 9点）</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>222例（手術112例、理学療法110例）。8か月時のデータは手術群100例（89%）、理学療法群88例（80%）</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>8か月時のHOS-ADLは手術群78.4（95%CI 74.4–82.3）、理学療法群69.2（65.2–73.3）。ベースラインHOS-ADL・年齢・性別・施設で調整後、手術群が10.0点高かった（95%CI 6.4–13.6、P&lt;.001）。重篤な有害事象はいずれの群もなし。結論：二次・三次医療に紹介された症候性FAIでは、鏡視下手術が理学療法＋活動修正より優れた成績</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：参加者の多くが調整センターから募集された（20例以上の施設では効果は一貫）／理学療法は最大8回とNHSの資源内で実施可能な範囲に限定しており、より多く・高頻度の介入なら成績が改善した可能性。加えてCE角&lt;20°は除外されているがBDDH（20–25°）は含まれうる（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/bmj.l185</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／手術療法</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="E34" s="13" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="12" t="n"/>
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Mansell NS, Rhon DI, Meyer J, Slevin JM, Marchant BG. 2018. Am J Sports Med 46(6):1306-1314</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Arthroscopic Surgery or Physical Therapy for Patients With Femoroacetabular Impingement Syndrome: A Randomized Controlled Trial With 2-Year Follow-up</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>大規模軍病院の整形外科に紹介された手術適応のFAIS患者（91.3%が現役軍人）</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>RCT（Level 1）／鏡視下手術 vs 理学療法（割付後3週以内に開始する監督下12回の外来プログラム）／2年間の疼痛・機能障害・改善の自覚を評価／主要アウトカム：HOS（ADL・Sport）、副次：iHOT-33、Global Rating of Change（GRC）、2年時の復職／当初の割付群で解析</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>適格104例中80例が参加</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>両群ともHOS・iHOT-33が有意改善したが、2年時の群間差は有意でなかった（HOS-ADL 3.8［95%CI −6.0〜13.6］、HOS-Sport 1.8［−11.2〜14.7］、iHOT-33 6.3［−6.1〜18.7］）。全体のGRC中央値は「ほぼ変わらない」（0）。手術群の2例は手術を受けず、理学療法群の28例は最終的に手術を受けた。実際の手術有無での感度分析でも結果は不変。2年時に手術例の33.3%、非手術例の33.3%が軍務不適で除隊。結論：2年時に両群に差はない</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>抄録明記：単一病院・単一術者／クロスオーバー率が高い。加えて軍人が大半で一般集団への外挿に限界（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/0363546517751912</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／手術療法</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="E35" s="13" t="n"/>
-      <c r="G35" s="14" t="n"/>
-      <c r="H35" s="12" t="n"/>
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Martin SD, Dean MC, Gillinov SM, Cherian NJ, Eberlin CT, Kucharik MP, Abraham PF, Nazal MR, Conaway WK, Quinlan NJ, Alpaugh K, Torabian KA. 2024. Am J Sports Med 52(10):2574-2585</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Hip Arthroscopy Versus Physical Therapy for the Treatment of Symptomatic Acetabular Labral Tears in Patients Older Than 40 Years: 24-Month Results From a Randomized Controlled Trial</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>OAが軽度（Tönnis grade 0–2）の40歳以上の症候性股関節唇損傷患者（倫理上、全例が3か月以上の保存療法無効という手術適応を満たす：原著本文）</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>単一術者・並行群RCT（Level 1）／鏡視下手術＋術後理学療法（SPT）vs 理学療法単独（PTA）を1:1割付／PTAで改善不十分なら14週以上の理学療法後に手術へクロスオーバー可（CO）／主要アウトカム：24か月時のiHOT-33・mHHS／ITT解析＋修正as-treated解析・treatment-failure解析</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>97例（SPT群52例、PTA群45例）</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>PTA群の32例（71.1%）が理学療法開始後平均5.10か月でクロスオーバー。ITT・修正as-treated解析とも、ほぼ全指標でSPT群がPTA群より優れた。treatment-failure解析ではSPT群・CO群がPTA群より大きく改善したが、SPT群とCO群の改善に有意差なし。THA移行率に群間差なし。結論：OAが軽度の40歳以上ではSPTがPTAより良好だが、術前に理学療法を追加しても手術成績は損なわれず、一部の患者は手術を回避できた</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：クロスオーバー率が71%と高くデータが交絡している／全例が手術適応を満たしていたためクロスオーバーが増えた可能性／治療の好みによるバイアスの可能性／40歳以上が対象のためTönnis grade 2を含めた／24か月で長期成績は不明</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/03635465241263595</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>保存療法／手術療法</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="E36" s="13" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="12" t="n"/>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Kemp JL, Scholes MJ, Smith AJ, Coburn SL, Johnston RRT, Jones DM, Girdwood MA, King MG, Mentiplay BF, De Oliveira Silva D, Pazzinatto M, Schache AG, Gomes DA, Coburn GM, Crossley KM. 2026. Br J Sports Med 60(13):951-961</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Physiotherapist-led treatment for femoroacetabular impingement syndrome (the PhysioFIRST study): an assessor-blinded, limited disclosure randomised controlled trial</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>18–50歳のFAIS患者</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>評価者盲検・limited disclosure・並行群優越性RCT／6か月間の理学療法士主導の標的筋力強化（STRENGTH）vs 標準化ストレッチ（STRETCH）を1:1割付／主要アウトカム：6か月時のiHOT-33変化量、GROC（疼痛・機能）／副次：GROCの2値化（改善/非改善）、股関節筋力／ITT解析</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>154例：STRENGTH群79例（女性53%、平均35±9歳）、STRETCH群75例（女性45%、平均36±9歳）</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>6か月時のiHOT-33変化量に群間差なし（平均差0.2、95%CI −5.9〜6.3）、GROC-疼痛（0.2、P=.23）・GROC-機能（0.3）も差なし。GROC-疼痛で「改善」はSTRENGTH群72% vs STRETCH群52%（OR 2.36、95%CI 1.15–4.84）。股関節筋力の改善はSTRENGTH群で大きかった。iHOT-33は両群とも臨床的に意味のある改善（STRENGTH 19.2点、STRETCH 20.8点）。結論：股関節関連QOLの改善でどちらかが優れるわけではないが、標的筋力強化は疼痛の自覚的改善と筋力で優れる</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：運動介入の性質上、参加者の真の盲検化は不可能（limited disclosureで対応）／他群の治療内容を知ることによるバイアスの可能性は否定できない。加えてプロトコル記載の副次アウトカムの一部は本論文に未掲載／BDDHを含むかと骨形態別の解析は抄録に記載なし</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/bjsports-2025-110986</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>保存療法</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="E37" s="13" t="n"/>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="12" t="n"/>
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Harris-Hayes M, Steger-May K, Bove AM, Foster SN, Mueller MJ, Clohisy JC, Fitzgerald GK. 2020. BMJ Open Sport Exerc Med 6(1):e000707</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Movement pattern training compared with standard strengthening and flexibility among patients with hip-related groin pain: results of a pilot multicentre randomised clinical trial</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>慢性の股関節関連鼠径部痛（hip-related groin pain）患者</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>多施設パイロットRCT／動作パターン練習（MoveTrain：日常課題での生体力学を最適化する課題特異的練習）vs 筋力強化・柔軟性（Standard）／12週で10回の来院＋ホームエクササイズ／主要：実行可能性（募集・継続・治療アドヒアランス・治療忠実度）、副次：HOOS、下肢運動学、股関節筋力</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>46例（男17例、女29例、29±5.3歳、BMI 25.6±6.3）</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>目標の募集を達成し、継続率91%、来院率93%、ホームエクササイズのアドヒアランス62%、理学療法士のプロトコル遵守90%。両群ともHOOSと筋力が臨床的に意味のある改善を示したが群間差なし（HOOS P≥.13、筋力P≥.34）。MoveTrainはStandardより片脚スクワット時の股関節内転（P=.016）・骨盤下制（P=.026）を大きく減少。有害事象なし。結論：大規模な多施設RCTは実施可能</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：実行可能性の検証が目的で、副次アウトカムの統計的な群間差は想定していない／非手術管理のMICは確立されていない。加えて小規模・短期（12週）・骨形態別の解析なし（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/bmjsem-2019-000707</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>保存療法</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="E38" s="13" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="12" t="n"/>
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Aoyama M, Ohnishi Y, Utsunomiya H, Kanezaki S, Takeuchi H, Watanuki M, Matsuda DK, Uchida S. 2019. Clin J Sport Med 29(4):267-275</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>A Prospective, Randomized, Controlled Trial Comparing Conservative Treatment With Trunk Stabilization Exercise to Standard Hip Muscle Exercise for Treating Femoroacetabular Impingement: A Pilot Study</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>組み入れ基準を満たした症候性FAIの女性患者（日本）</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>前向きパイロットRCT（Level I）／標準的な股関節筋エクササイズに体幹安定化エクササイズを追加した群 vs 標準的な股関節筋エクササイズのみの対照群／介入前と4・8週後に股関節可動域、ハンドヘルドダイナモメーターによる等尺性筋力、mHHS・Vail hip score・iHOT-12を評価</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>20例（体幹安定化群10股、対照群10股）</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>体幹安定化群では介入4週で股関節屈曲可動域が対照群より有意に改善（P&lt;.05）。外転筋力は体幹安定化群で4週に有意改善し、対照群では改善なし（P&lt;.05）。8週時のiHOT-12（78.7±22.4 vs 53.0±22.3、P&lt;.01）とVail hip score（81.6±18.5 vs 61.1±11.6、P&lt;.05）は体幹安定化群で有意に高値。mHHSは4・8週とも群間差なし。結論：典型的な股関節リハビリに体幹安定化エクササイズを加えると短期成績が改善</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：症例数が少なく短期追跡／サンプルサイズ設計（検出力分析）を行っていない／体幹安定化群で疼痛期間が短い傾向（有意差なし）／男性を除外しており性別を超えて一般化できない。加えて骨形態（臼蓋被覆）別の解析なし</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1097/JSM.0000000000000516</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>保存療法</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="E39" s="13" t="n"/>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="12" t="n"/>
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Mortensen L, Schultz J, Elsner A, Jakobsen SS, Søballe K, Jacobsen JS, Kierkegaard S, Dalgas U, Mechlenburg I. 2018. J Rehabil Med 50(8):751-758</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Progressive resistance training in patients with hip dysplasia: A feasibility study</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>PAOを予定している症候性の股関節形成不全患者</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>実行可能性研究／8週間（20回）の監督下漸増抵抗トレーニング／トレーニングのアドヒアランス、脱落数、有害事象、VAS疼痛を記録／HAGOS、2種類のホップテスト、等速性ダイナモメーターによる股関節ピークトルクを評価</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>17例（年齢中央値28歳、22–40歳）</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>トレーニングのアドヒアランスは90.3±9%。有害事象は少なく軽微で、脱落1例、介入中の疼痛は許容範囲。HAGOSは6下位尺度中4つで改善（P&lt;.05）。立ち幅跳び12.2%（95%CI 1.3–23.0）、カウンタームーブメントジャンプ25.1%（95%CI 1.3–48.8）改善。患側の等速性求心性股関節屈曲ピークトルクが16.6%（95%CI 4.6–28.6）改善、健側の等尺性股関節屈曲も10.9%改善。結論：形成不全患者に対する監督下漸増抵抗トレーニングは実行可能で、疼痛・PRO・機能・股関節屈筋力を改善しうる</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>対照群のない実行可能性研究で有効性は検証できない／17例と小規模で8週の短期評価／PAO待機例のみでBDDHに限定されず、Cam有無の評価なし（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2340/16501977-2371</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>保存療法</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="E40" s="13" t="n"/>
-      <c r="G40" s="14" t="n"/>
-      <c r="H40" s="12" t="n"/>
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Probst DT, Sookochoff MF, Harris-Hayes M, Prather H, Lipsey KL, Cheng AL. 2023. J Orthop Sports Phys Ther 53(5):286-306</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>What is the Rate of Response to Nonoperative Treatment for Hip-Related Pain? A Systematic Review With Meta-analysis</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>FAIS・臼蓋形成不全・股関節唇損傷・特定されない非関節症性股関節痛の患者を対象に、非手術療法と他の治療を比較したRCTと前向きコホート研究</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>システマティックレビュー＋メタ解析／7データベースと参考文献を開始時から2022年2月まで検索／ランダム効果メタ解析／改変Downs and Blackチェックリストで研究の質、GRADEでエビデンスの確実性を評価</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>26研究（1,153例）を質的統合、うち16研究をメタ解析</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>非手術療法への全体の満足な反応率は54%（95%CI 32–76%、確実性は中等度）。理学療法後の平均改善は100点満点の股関節症状尺度で11.3点（7.6–14.9、確実性は低〜中等度）、疼痛重症度尺度で22.2点（4.6–39.9、低）。治療期間や手法（柔軟性運動・動作パターン練習・モビライゼーション）による特異的な効果は確認できなかった（非常に低〜低）。ヒアルロン酸注射・ステロイド注射・装具を支持するエビデンスは非常に低〜低。結論：非関節症性股関節痛の半数以上が非手術療法に満足な反応を示すが、包括的非手術療法の必須要素は不明</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：Cochraneのバイアスリスク評価（RoB 2、ROBINS-I）ならより高いバイアスリスクと判定された可能性／統合は既存エビデンスの量・質・異質性によって制限される。加えて疾患別（形成不全・Cam有無）の反応率は抄録に記載なし</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2519/jospt.2023.11666</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>保存療法</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="E41" s="13" t="n"/>
-      <c r="G41" s="14" t="n"/>
-      <c r="H41" s="12" t="n"/>
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Kemp JL, Risberg MA, Mosler A, Harris-Hayes M, Serner A, Moksnes H, et al. 2020. Br J Sports Med 54(9):504-511</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Physiotherapist-led treatment for young to middle-aged active adults with hip-related pain: consensus recommendations from the International Hip-related Pain Research Network, Zurich 2018</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>若年〜中年の活動的な成人の股関節関連疼痛に対する理学療法士主導の治療（専門家38名によるコンセンサス）</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>コンセンサス声明（International Hip-related Pain Research Network, Zurich 2018）／別途行ったシステマティックレビューに基づく推奨案を事前配布し、会議で議論・修正・投票</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>専門研究者・臨床家38名</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>臨床推奨6項目・研究推奨5項目がすべてコンセンサスを得た。臨床推奨：①股関節関連疼痛には運動を基本とした治療を推奨、②運動療法は少なくとも3か月行う、③股関節手術後は理学療法士主導のリハを行う、④PROM・身体機能障害・心理社会的因子の評価で治療反応をモニターする、⑤身体活動（スポーツを含む）を推奨、⑥患者の期待を話し合い、共同意思決定と教育を行う。研究推奨：運動プログラムの負荷・回数・セット・期間などの詳細な報告、最適な頻度・強度・時間・種類・量・漸増の検討、患者教育の効果の検討、その他の治療（徒手療法・薬物・注射）の効果の検討、併存疾患と社会的決定要因の影響の検討など</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>専門家の合意であり高いエビデンスレベルではない（基盤となったSRでも理学療法の強いエビデンスは不足と記載）／臼蓋形成不全・Camなど骨形態別の推奨ではない（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/bjsports-2019-101458</t>
+        </is>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>保存療法</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="E42" s="13" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="12" t="n"/>
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Reiman MP, Agricola R, Kemp JL, Heerey JJ, Weir A, van Klij P, et al. 2020. Br J Sports Med 54(11):631-641</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Consensus recommendations on the classification, definition and diagnostic criteria of hip-related pain in young and middle-aged active adults from the International Hip-related Pain Research Network, Zurich 2018</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>若年〜中年の活動的な成人の股関節関連疼痛の分類・定義・診断基準（専門家37名のパネル）</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>コンセンサス声明（International Hip-related Pain Research Network, Zurich 2018）／2018年6月のスコーピングレビューに基づくエビデンス声明を作成し、専門家パネルで議論・合意</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>専門家37名</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>非筋骨格系・重篤な疾患（腫瘍・感染・疲労骨折・大腿骨頭すべり症など）と競合する筋骨格系疾患（腰椎など）を除外したうえで、股関節関連疼痛の主な病態を①FAI症候群、②臼蓋形成不全および/または股関節不安定性、③明確な骨形態を伴わない病態（関節唇・軟骨・円靱帯）の3つに分類し、研究と臨床でこの用語を使うことを推奨。臨床検査・画像の診断的有用性は限られ、包括的評価が必要。FADIR陰性は除外に役立つが有用性は限定的。初期画像は骨盤正面像と大腿骨頭頸部の側面像とし、詳細な画像は必要時のみ。研究では骨形態の定義・計測・統計報告を明確に統一すべき</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>専門家の合意であり高いエビデンスレベルではない／BDDHのようにFAIと不安定性の両方を持つ境界例の扱いは抄録に記載なし（デザイン由来、要原著Discussion確認）</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/bjsports-2019-101453</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>病態</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="E43" s="13" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="12" t="n"/>
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Jacobsen JS, Hölmich P, Thorborg K, Bolvig L, Jakobsen SS, Søballe K, Mechlenburg I. 2018. J Hip Preserv Surg 5(1):39-46</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Muscle-tendon-related pain in 100 patients with hip dysplasia: prevalence and associations with self-reported hip disability and muscle strength</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>股関節形成不全患者</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>横断研究／clinical entity approach（触診・抵抗時痛など）で筋腱由来の疼痛を同定／HAGOSによる自己報告の股関節機能障害、ハンドヘルドダイナモメーターによる筋力との関連を、年齢・性別で調整した重回帰分析で検討</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>100例（男17例、平均29±9歳）</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>腸腰筋関連痛（56%、95%CI 46–66）と外転筋関連痛（42%、95%CI 32–52）が最も多く、内転筋・ハムストリングス・腹直筋関連痛は少なかった。筋腱由来の疼痛はHAGOSと有意な負の関連（調整後 −3.35〜−7.51点、P&lt;.05）。股関節伸展以外でも筋力と有意な負の関連（−0.11〜−0.12 Nm/kg、P&lt;.05）。結論：形成不全患者の約半数に筋腱由来の疼痛があり、特に腸腰筋と外転筋に多く、機能障害と筋力低下に関連する</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：clinical entity approachの検者間信頼性は軽度〜中等度の一致にとどまる／筋力測定は検者依存で測定誤差がある／対照群がない。加えて横断研究で因果関係は不明／Cam有無の評価なし</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1093/jhps/hnx041</t>
+        </is>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>病態</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="E44" s="13" t="n"/>
-      <c r="G44" s="14" t="n"/>
-      <c r="H44" s="12" t="n"/>
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Tang J, Boel F, van Buuren MM, Riedstra NS, van den Berg MA, Ahedi H, et al. 2026. Br J Sports Med 60(1):28-35</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Cam morphology and the risk of developing radiographic hip osteoarthritis within 8 years: an individual participant data meta-analysis of 23 886 hips from the world COACH consortium</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>World COACH consortiumのコホートのうち、ベースラインで画像上の股関節OAがなく、4–8年の追跡がある股関節</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>個別参加者データ（IPD）メタ解析／骨盤正面像でα角を統一的に計測し、α角≥60°をcam形態と定義／画像上のOAの新規発症との関連を3階層混合効果ロジスティック回帰（左右・個人・コホートの変動を考慮）で解析／年齢・性別・BMI別のサブグループ解析</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>23,886股（平均62.2±8.4歳、女性70.6%、BMI 27.4±4.5、平均追跡6.1±3.0年）</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>cam形態は画像上のOA発症と関連（OR 1.87、95%CI 1.36–2.59）、α角が大きいほどリスク増加（1度ごとにOR 1.02、95%CI 1.01–1.03）。cam形態によるOA発症の相対リスクは全体で1.62（95%CI 1.26–2.07）、51–60歳で最大（2.15）、男性（2.50）で女性（1.75）より高い。結論：cam形態を有する股関節は4–8年以内のOA発症リスクが高く、一次・二次予防の標的となりうる</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>原著記載：cam形態の定量を骨盤正面像のみに依存しており、MRI・CTよりα角とcamの有病率を過小評価する可能性（性差もありうる）／人種のデータがない／平均62歳で40歳未満への適用に限界／臼蓋形成不全やpincer形態の影響を考慮していない</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1136/bjsports-2025-110144</t>
+        </is>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>疫学</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="E45" s="13" t="n"/>
@@ -6815,6 +7655,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
